--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-alert.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-alert.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>Priorite</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): hl7:Flag-priority-code</t>
@@ -3006,10 +3009,10 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3047,10 +3050,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3073,13 +3076,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3130,7 +3133,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3147,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3173,13 +3176,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3230,7 +3233,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
